--- a/output/pdf_financials_xlsx/SXGC.xlsx
+++ b/output/pdf_financials_xlsx/SXGC.xlsx
@@ -4548,16 +4548,16 @@
         <v>0</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>0.016412</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>-0.431946</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>-0.602677</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>-2.086628</v>
       </c>
     </row>
     <row r="92">
@@ -4567,40 +4567,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>6.016717</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>6.069717</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>6.071217</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>6.958017</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>7.125361</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>7.969961</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>9.115859</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>9.182529000000001</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>9.402625</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>10.683524</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>9.382338000000001</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>13.973409</v>
       </c>
     </row>
     <row r="93">
@@ -7832,7 +7832,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -7966,7 +7970,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -13368,7 +13376,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E96" s="5" t="n">
         <v>6.016717</v>
       </c>
@@ -13504,7 +13516,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SXGC.xlsx
+++ b/output/pdf_financials_xlsx/SXGC.xlsx
@@ -910,22 +910,22 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.148237</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.067566</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.130781</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.045434</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.091642</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.172807</v>
       </c>
       <c r="M12" s="1" t="inlineStr">
         <is>
@@ -1693,22 +1693,22 @@
         <v>-2.4413</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.574097</v>
+        <v>-3.722334</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.40134</v>
+        <v>-2.468906</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.941081</v>
+        <v>-3.071862</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-4.145387</v>
+        <v>-4.190821</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-6.635579</v>
+        <v>-6.727221</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-47.374411</v>
+        <v>-47.547218</v>
       </c>
       <c r="M27" s="1" t="inlineStr">
         <is>
@@ -1783,22 +1783,22 @@
         <v>-2.41612</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.55073</v>
+        <v>-3.698967</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.382531</v>
+        <v>-2.450097</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.905491</v>
+        <v>-3.036272</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-4.1034</v>
+        <v>-4.148834</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-6.572765</v>
+        <v>-6.664407</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-47.218282</v>
+        <v>-47.391089</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -1999,34 +1999,34 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>5.376279</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>4.371419</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>4.087254</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>4.921999</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>11.398105</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.839544</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>18.906515</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>7.386407</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>12.141196</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>14.680432</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>15.497519</v>
@@ -2085,34 +2085,34 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>5.376279</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>4.371419</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>4.087254</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>4.921999</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>11.398105</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.839544</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>18.906515</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>7.386407</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>12.141196</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>14.680432</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>15.497519</v>
@@ -2601,34 +2601,34 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>5.466361</v>
+        <v>0.090082</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>4.448757</v>
+        <v>0.077338</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4.228716</v>
+        <v>0.141462</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>5.541839</v>
+        <v>0.6198399999999999</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>11.935422</v>
+        <v>0.537317</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.301845</v>
+        <v>0.462301</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>19.191277</v>
+        <v>0.284762</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>7.666381</v>
+        <v>0.279974</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>12.412612</v>
+        <v>0.271416</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>14.992588</v>
+        <v>0.312156</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.367383</v>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
@@ -21772,7 +21772,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">

--- a/output/pdf_financials_xlsx/SXGC.xlsx
+++ b/output/pdf_financials_xlsx/SXGC.xlsx
@@ -5403,7 +5403,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.008251</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -19386,7 +19386,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SXGC.xlsx
+++ b/output/pdf_financials_xlsx/SXGC.xlsx
@@ -1326,10 +1326,10 @@
         <v>-4.145387</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-6.635579</v>
+        <v>-5.967378</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-47.374411</v>
+        <v>-7.918182</v>
       </c>
       <c r="M20" s="1" t="inlineStr">
         <is>
@@ -1371,10 +1371,10 @@
         <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>-0.668201</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0</v>
+        <v>-39.456229</v>
       </c>
       <c r="M21" s="1" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.08464000000000001</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
@@ -18710,7 +18710,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -18786,7 +18790,11 @@
           <t>Net proceeds from Southern Cross private placement</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -22104,7 +22112,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -22178,7 +22190,11 @@
           <t>Loss from discontinued operations 4</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
